--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
+        <v>שיר אמלי - אזמהניה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410257&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410260&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-29</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
+        <v>שיר אמלי - אזמהניה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתי שקד - גשם</v>
+        <v>רשל רובין - יש לי כוח</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410256&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410259&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-29</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתי שקד - גשם</v>
+        <v>רשל רובין - יש לי כוח</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>לידור עמירה - חלום</v>
+        <v>עברי לידר - ביונסה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410255&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410258&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-29</v>
@@ -545,164 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>לידור עמירה - חלום</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410254&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ישראל מועלמי - דור מלא נסיונות</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410253&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ישראל מועלמי - דור מלא נסיונות</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יונתן רזאל - היינו כחולמים</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410252&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יונתן רזאל - היינו כחולמים</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>בר סיידו - הימים שאחריך</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410251&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>בר סיידו - הימים שאחריך</v>
+        <v>עברי לידר - ביונסה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר אמלי - אזמהניה</v>
+        <v>שי וינר - יבוא שלום</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410260&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410287&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר אמלי - אזמהניה</v>
+        <v>שי וינר - יבוא שלום</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רשל רובין - יש לי כוח</v>
+        <v>שחר גזנלי - 2 כוסות יין</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410259&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410286&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רשל רובין - יש לי כוח</v>
+        <v>שחר גזנלי - 2 כוסות יין</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עברי לידר - ביונסה</v>
+        <v>קול החברים - מחרוזת רוקדת בלילות 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410258&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410285&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,12 +545,886 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עברי לידר - ביונסה</v>
+        <v>קול החברים - מחרוזת רוקדת בלילות 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עמית סמוכי - ראויה לאהבה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410284&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עמית סמוכי - ראויה לאהבה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עופר בדיחי - בצל עצי התאנה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410283&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עופר בדיחי - בצל עצי התאנה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>סטפן לגר - מינימום</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410282&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>סטפן לגר - מינימום</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נוי אביטל - ההצגה חייבת להימשך</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410281&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נוי אביטל - ההצגה חייבת להימשך</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>מנשה סביליה - מחרוזת אם קצת עצוב 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410280&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>מנשה סביליה - מחרוזת אם קצת עצוב 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>מינקובסקי - מכלוף</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410279&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>מינקובסקי - מכלוף</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>מאור אברהם - כל הלילה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410278&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>מאור אברהם - כל הלילה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>מאור אברהם - הלב הזה שלך</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410277&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>מאור אברהם - הלב הזה שלך</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>יוסף נטיב - אנשים כאלה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410276&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>יוסף נטיב - אנשים כאלה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>יוסי שטרית - חורף אחד בלעדייך</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410275&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>יוסי שטרית - חורף אחד בלעדייך</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>האחים אהרון - השם ישמרך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410274&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>האחים אהרון - השם ישמרך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>בני אלבז - עם פלדה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410273&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>בני אלבז - עם פלדה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אריאל רביבו - גאולה</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410272&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אריאל רביבו - גאולה</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אריאל לוי - מחרוזת שמח בני 2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410271&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אריאל לוי - מחרוזת שמח בני 2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>תמר אופיר - בדמייך חיי</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410270&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>תמר אופיר - בדמייך חיי</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>ליאל נחתום - שערי שמים פתח</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410269&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>ליאל נחתום - שערי שמים פתח</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>הראל סקעת - אמונה שבורה</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410268&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>הראל סקעת - אמונה שבורה</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>החצר האחורית של ג'וני - לבד</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410267&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>החצר האחורית של ג'וני - לבד</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>הודיה בנישו - בינתיים</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410266&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>הודיה בנישו - בינתיים</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>אליהו חייט - אני קורא לך</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C24" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410265&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>אליהו חייט - אני קורא לך</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>אור סלמן - הלב הטוב ינצח</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C25" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410264&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>אור סלמן - הלב הטוב ינצח</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>אהרון ירימי &amp; ששי יעיש - אביר ישראל 2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C26" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410263&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>אהרון ירימי &amp; ששי יעיש - אביר ישראל 2026</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>אביר יעקב - עד מתי נעצור</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C27" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410262&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>אביר יעקב - עד מתי נעצור</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L27"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אהרן רזאל &amp; הרב שלמה כ"ץ - ועשו לי מקדש</v>
+        <v>ישראל ורולקר - אנא אל חי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410290&amp;sid=7985c882a7deca566a6f288096b142ba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410298&amp;sid=cd57821f7a473b351f987152c916e91c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אהרן רזאל &amp; הרב שלמה כ"ץ - ועשו לי מקדש</v>
+        <v>ישראל ורולקר - אנא אל חי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אדרת - ושמחת בחגך</v>
+        <v>ישי ריבו - לא לחינם</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410289&amp;sid=7985c882a7deca566a6f288096b142ba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410297&amp;sid=cd57821f7a473b351f987152c916e91c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אדרת - ושמחת בחגך</v>
+        <v>ישי ריבו - לא לחינם</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אברהם אביב אלוש - אז ישיר (שבת מכל הסיבות)</v>
+        <v>יניב חיו &amp; שמואל דנה - חיזרי אליי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410288&amp;sid=7985c882a7deca566a6f288096b142ba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410296&amp;sid=cd57821f7a473b351f987152c916e91c</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-31</v>
@@ -545,12 +545,202 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אברהם אביב אלוש - אז ישיר (שבת מכל הסיבות)</v>
+        <v>יניב חיו &amp; שמואל דנה - חיזרי אליי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יוחאי אביטן - בן טוב</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410295&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יוחאי אביטן - בן טוב</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>גיא זו-ארץ &amp; רועי זו-ארץ - והיא שעמדה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410294&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>גיא זו-ארץ &amp; רועי זו-ארץ - והיא שעמדה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>בנצ'ו - מודה לבורא</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410293&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>בנצ'ו - מודה לבורא</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>איתי בירמן &amp; בן ארצי - נלחמתי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410292&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>איתי בירמן &amp; בן ארצי - נלחמתי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אילן חדד - מחרוזת חפלה 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410291&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אילן חדד - מחרוזת חפלה 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ישראל ורולקר - אנא אל חי</v>
+        <v>צח חכים - זמן אחר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410298&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410302&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ישראל ורולקר - אנא אל חי</v>
+        <v>צח חכים - זמן אחר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ישי ריבו - לא לחינם</v>
+        <v>נתי לוי לב - רמי לוי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410297&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410301&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ישי ריבו - לא לחינם</v>
+        <v>נתי לוי לב - רמי לוי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יניב חיו &amp; שמואל דנה - חיזרי אליי</v>
+        <v>מוריה מעטוף - בואי לאהוב איתי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410296&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410300&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-31</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יניב חיו &amp; שמואל דנה - חיזרי אליי</v>
+        <v>מוריה מעטוף - בואי לאהוב איתי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יוחאי אביטן - בן טוב</v>
+        <v>מור דהרי &amp; אריאל קנדאבי &amp; ארין קנדאבי &amp; אסף פפל - שמע ישראל</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410295&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410299&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-31</v>
@@ -583,164 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יוחאי אביטן - בן טוב</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>גיא זו-ארץ &amp; רועי זו-ארץ - והיא שעמדה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410294&amp;sid=cd57821f7a473b351f987152c916e91c</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>גיא זו-ארץ &amp; רועי זו-ארץ - והיא שעמדה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>בנצ'ו - מודה לבורא</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410293&amp;sid=cd57821f7a473b351f987152c916e91c</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>בנצ'ו - מודה לבורא</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>איתי בירמן &amp; בן ארצי - נלחמתי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410292&amp;sid=cd57821f7a473b351f987152c916e91c</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>איתי בירמן &amp; בן ארצי - נלחמתי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אילן חדד - מחרוזת חפלה 2026</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410291&amp;sid=cd57821f7a473b351f987152c916e91c</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אילן חדד - מחרוזת חפלה 2026</v>
+        <v>מור דהרי &amp; אריאל קנדאבי &amp; ארין קנדאבי &amp; אסף פפל - שמע ישראל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צח חכים - זמן אחר</v>
+        <v>נותי פוקס &amp; משולם זושא - קרב יום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410302&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410307&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צח חכים - זמן אחר</v>
+        <v>נותי פוקס &amp; משולם זושא - קרב יום</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתי לוי לב - רמי לוי</v>
+        <v>יוסי אזולאי מארח אמנים - אני מאמין</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410301&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410306&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתי לוי לב - רמי לוי</v>
+        <v>יוסי אזולאי מארח אמנים - אני מאמין</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מוריה מעטוף - בואי לאהוב איתי</v>
+        <v>זהבה כהן - Azadi</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410300&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410305&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-31</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מוריה מעטוף - בואי לאהוב איתי</v>
+        <v>זהבה כהן - Azadi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מור דהרי &amp; אריאל קנדאבי &amp; ארין קנדאבי &amp; אסף פפל - שמע ישראל</v>
+        <v>דייויד טויב &amp; מוישלה שניידר &amp; גיל ישראלוב - חד גדיא</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410299&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410304&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-31</v>
@@ -583,12 +583,50 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מור דהרי &amp; אריאל קנדאבי &amp; ארין קנדאבי &amp; אסף פפל - שמע ישראל</v>
+        <v>דייויד טויב &amp; מוישלה שניידר &amp; גיל ישראלוב - חד גדיא</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>איתמר ועקנין - בֶּאֱמוּנָה שְׁלֵמָה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410303&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>איתמר ועקנין - בֶּאֱמוּנָה שְׁלֵמָה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נותי פוקס &amp; משולם זושא - קרב יום</v>
+        <v>עידן צ'או - תשע נשמות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410307&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410312&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נותי פוקס &amp; משולם זושא - קרב יום</v>
+        <v>עידן צ'או - תשע נשמות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יוסי אזולאי מארח אמנים - אני מאמין</v>
+        <v>עומר קורן מארח את קובארי - שום דבר לא יכול לקרות</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410306&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410311&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יוסי אזולאי מארח אמנים - אני מאמין</v>
+        <v>עומר קורן מארח את קובארי - שום דבר לא יכול לקרות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>זהבה כהן - Azadi</v>
+        <v>מוקולי - מציאות מסוכנת</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410305&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410310&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-31</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>זהבה כהן - Azadi</v>
+        <v>מוקולי - מציאות מסוכנת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>דייויד טויב &amp; מוישלה שניידר &amp; גיל ישראלוב - חד גדיא</v>
+        <v>מועדון הקצב של אביהו פנחסוב - לא מפחד לרקוד</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410304&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410309&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-31</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>דייויד טויב &amp; מוישלה שניידר &amp; גיל ישראלוב - חד גדיא</v>
+        <v>מועדון הקצב של אביהו פנחסוב - לא מפחד לרקוד</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>איתמר ועקנין - בֶּאֱמוּנָה שְׁלֵמָה</v>
+        <v>טוני ג'ינו עם קלארק רוזנברג &amp; ג'אמבר - מסתכלת עליי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410303&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410308&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-31</v>
@@ -621,7 +621,7 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>איתמר ועקנין - בֶּאֱמוּנָה שְׁלֵמָה</v>
+        <v>טוני ג'ינו עם קלארק רוזנברג &amp; ג'אמבר - מסתכלת עליי</v>
       </c>
     </row>
   </sheetData>
